--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_decimal_place_correction.xlsx
@@ -744,14 +744,14 @@
       <c r="E4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>81.7</v>
+      <c r="F4" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -760,13 +760,13 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.4</v>
@@ -775,21 +775,21 @@
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>19.1</v>
+      <c r="S4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -798,7 +798,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -836,7 +836,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -850,8 +850,8 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>119.4</v>
+      <c r="M5" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -877,11 +877,11 @@
       <c r="U5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>13.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -890,7 +890,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -911,43 +911,43 @@
       <c r="D6" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="E6" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="R6" s="3" t="n">
@@ -960,22 +960,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V6" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>12.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>9</v>
@@ -1012,25 +1012,25 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="8" t="n">
+      <c r="M7" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>19.3</v>
@@ -1039,10 +1039,10 @@
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
@@ -1053,14 +1053,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1082,19 +1082,19 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1117,8 +1117,8 @@
       <c r="P8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>27.4</v>
+      <c r="Q8" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.4</v>
@@ -1127,18 +1127,18 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>128.9</v>
@@ -1173,10 +1173,10 @@
         <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1191,7 +1191,7 @@
         <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>551.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1204,10 +1204,10 @@
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.3</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.8</v>
@@ -1264,8 +1264,8 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
@@ -1274,7 +1274,7 @@
       <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1287,13 +1287,13 @@
         <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>117.7</v>
+        <v>27.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.7</v>
@@ -1333,29 +1333,29 @@
       <c r="E11" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <v>18.6</v>
+      <c r="G11" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1366,19 +1366,19 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>14.4</v>
+      <c r="S11" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="3" t="n">
@@ -1387,11 +1387,11 @@
       <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="8" t="n">
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>25.9</v>
@@ -1418,28 +1418,28 @@
       <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="G12" s="8" t="n">
+      <c r="F12" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1454,11 +1454,11 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="8" t="n">
-        <v>12.9</v>
+      <c r="S12" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>37</v>
@@ -1500,7 +1500,7 @@
       <c r="D13" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1510,13 +1510,13 @@
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1525,16 +1525,16 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>18.9</v>
@@ -1546,18 +1546,18 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>185.4</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X13" s="8" t="n">
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1585,10 +1585,10 @@
       <c r="D14" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1597,19 +1597,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1619,19 +1619,19 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
@@ -1639,10 +1639,10 @@
       <c r="V14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="8" t="n">
+      <c r="W14" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1671,13 +1671,13 @@
         <v>26</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>50.8</v>
+        <v>11</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1686,19 +1686,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1709,19 +1709,19 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V15" s="8" t="n">
+      <c r="U15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1754,7 +1754,7 @@
         <v>128</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>568.1</v>
+        <v>568.8</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>92.5</v>
@@ -1775,7 +1775,7 @@
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5.9</v>
+        <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
@@ -1784,13 +1784,13 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1111</v>
+        <v>111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
@@ -1799,16 +1799,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>958.2</v>
+        <v>98.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.9</v>
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1851,38 +1851,38 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>29.4</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>362</v>
+        <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>18.2</v>
@@ -1890,17 +1890,17 @@
       <c r="V17" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="8" t="n">
-        <v>16.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>872.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>25.9</v>
@@ -1924,17 +1924,17 @@
       <c r="E18" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>13</v>
+      <c r="F18" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1942,13 +1942,13 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>24.4</v>
+      <c r="L18" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
@@ -1961,31 +1961,31 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="8" t="n">
-        <v>19.6</v>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2054,8 +2054,8 @@
       <c r="T19" s="3" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>7.2</v>
+      <c r="U19" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
@@ -2091,10 +2091,10 @@
       <c r="D20" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="E20" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2103,11 +2103,11 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
@@ -2115,14 +2115,14 @@
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>214</v>
-      </c>
-      <c r="N20" s="8" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2131,7 +2131,7 @@
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>15.3</v>
@@ -2139,16 +2139,16 @@
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="8" t="n">
-        <v>222.4</v>
+      <c r="U20" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="8" t="n">
+      <c r="W20" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
@@ -2176,11 +2176,11 @@
       <c r="D21" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <v>2.7</v>
+      <c r="E21" s="3" t="n">
+        <v>12.7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>12.1</v>
@@ -2192,22 +2192,22 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2225,7 +2225,7 @@
         <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>19.8</v>
@@ -2233,8 +2233,8 @@
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="8" t="n">
-        <v>0.9</v>
+      <c r="X21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2256,22 +2256,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>429</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>26.9</v>
+      <c r="E22" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2280,19 +2280,19 @@
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2307,7 +2307,7 @@
         <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>149.5</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2318,14 +2318,14 @@
       <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="X22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+        <v>13.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2341,28 +2341,28 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
+        <v>2320.3</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>112.1</v>
+        <v>132.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>50.1</v>
+        <v>56.7</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
+        <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.3</v>
@@ -2371,13 +2371,13 @@
         <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>11.4</v>
@@ -2386,10 +2386,10 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2431,13 +2431,13 @@
       <c r="D24" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G24" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2447,10 +2447,10 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
@@ -2459,7 +2459,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2470,23 +2470,23 @@
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>17.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>17.2</v>
@@ -2522,44 +2522,44 @@
       <c r="F25" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <v>10.9</v>
+      <c r="G25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>10.7</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>2.9</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2570,10 +2570,10 @@
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>24.4</v>
@@ -2613,59 +2613,59 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="8" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2684,16 +2684,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>11.7</v>
+        <v>25.1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>24</v>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2702,10 +2702,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>12.4</v>
@@ -2722,20 +2722,20 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.4</v>
@@ -2743,11 +2743,11 @@
       <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="X27" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2771,17 +2771,17 @@
       <c r="D28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="8" t="n">
-        <v>11.5</v>
+      <c r="E28" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>15.9</v>
+      <c r="G28" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2793,9 +2793,9 @@
         <v>5.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2828,14 +2828,14 @@
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>17.8</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2851,19 +2851,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2887,22 +2887,22 @@
         <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>27.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2914,10 +2914,10 @@
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>11.2</v>
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>13.1</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>527.1</v>
+        <v>52.1</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>91.7</v>
@@ -2951,7 +2951,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -2966,7 +2966,7 @@
         <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.7</v>
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -2990,7 +2990,7 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="8" t="n">
-        <v>101.9</v>
+      <c r="E31" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>18.3</v>
@@ -3046,13 +3046,13 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3063,29 +3063,29 @@
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>111.4</v>
+      <c r="U31" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>165.8</v>
@@ -3112,8 +3112,8 @@
       <c r="E32" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>19.9</v>
+      <c r="F32" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>17.7</v>
@@ -3128,15 +3128,15 @@
         <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.5</v>
+        <v>10.5</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3145,17 +3145,17 @@
       <c r="P32" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q32" s="8" t="n">
-        <v>264.6</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S32" s="8" t="n">
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>18.8</v>
       </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="T32" s="3" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="n">
@@ -3164,12 +3164,12 @@
       <c r="W32" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>17.2</v>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3190,20 +3190,20 @@
       <c r="D33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3215,10 +3215,10 @@
         <v>14.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.5</v>
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3229,7 +3229,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3239,15 +3239,15 @@
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3270,28 +3270,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>89</v>
+      <c r="F34" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>14.7</v>
+      <c r="H34" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
@@ -3302,8 +3302,8 @@
       <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3324,19 +3324,19 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
+      <c r="X34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3391,7 +3391,7 @@
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
@@ -3402,7 +3402,7 @@
       <c r="R35" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
@@ -3411,17 +3411,17 @@
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3445,8 +3445,8 @@
       <c r="D36" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <v>10.9</v>
+      <c r="E36" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>18.3</v>
@@ -3458,43 +3458,43 @@
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>8.6</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>19.8</v>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.7</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
@@ -3502,8 +3502,8 @@
       <c r="W36" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>3.3</v>
+      <c r="X36" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>55</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>128.5</v>
@@ -3537,22 +3537,22 @@
         <v>94.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>64.2</v>
@@ -3568,13 +3568,13 @@
         <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3586,10 +3586,10 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>25.7</v>
@@ -3628,10 +3628,12 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>13</v>
       </c>
@@ -3642,7 +3644,7 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>298.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
@@ -3650,17 +3652,17 @@
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="8" t="n">
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>128.9</v>
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
@@ -3668,11 +3670,11 @@
       <c r="W38" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3694,22 +3696,22 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E39" s="8" t="n">
+        <v>269.2</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>11</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3718,21 +3720,21 @@
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <v>14.9</v>
+      <c r="N39" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3740,16 +3742,16 @@
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>51.7</v>
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>14.6</v>
@@ -3758,7 +3760,7 @@
         <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3774,7 +3776,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>27.2</v>
@@ -3803,17 +3805,17 @@
       <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>22</v>
@@ -3821,22 +3823,22 @@
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="8" t="n">
+      <c r="S40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>169.5</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y40" s="3" t="n">
@@ -3861,26 +3863,26 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="8" t="n">
-        <v>289.4</v>
+      <c r="D41" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -3892,21 +3894,21 @@
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3918,8 +3920,8 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="8" t="n">
-        <v>181.5</v>
+      <c r="W41" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>16.3</v>
@@ -3928,7 +3930,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3956,13 +3958,13 @@
         <v>19.3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>125.7</v>
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -3971,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -3988,16 +3990,16 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="8" t="n">
+      <c r="R42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="V42" s="3" t="n">
@@ -4099,7 +4101,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
+        <v>1911.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>109.7</v>
@@ -4111,19 +4113,19 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>107.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>44</v>
@@ -4132,13 +4134,13 @@
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4156,13 +4158,13 @@
         <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>831.9</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4192,7 +4194,7 @@
       <c r="E46" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G46" s="3" t="n">
@@ -4205,13 +4207,13 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>111.7</v>
+        <v>52.1</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>10.7</v>
@@ -4220,10 +4222,10 @@
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>24.7</v>
@@ -4231,7 +4233,7 @@
       <c r="R46" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="8" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4247,13 +4249,13 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>265.7</v>
+        <v>65.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
